--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
   </si>
   <si>
     <t>В0587ВТ</t>
@@ -125,8 +116,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -212,11 +204,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -224,9 +217,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -580,20 +573,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46150</v>
       </c>
       <c r="B2">
         <v>1158</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>25.892</v>
@@ -611,7 +604,7 @@
         <v>21.49</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -621,20 +614,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46153</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>21.708</v>
@@ -652,7 +645,7 @@
         <v>33.43</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -662,20 +655,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2">
+        <v>46153</v>
       </c>
       <c r="B4">
         <v>1148</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -693,7 +686,7 @@
         <v>15.4</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -703,20 +696,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="A5" s="2">
+        <v>46156</v>
       </c>
       <c r="B5">
         <v>1148</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>22.593</v>
@@ -734,7 +727,7 @@
         <v>18.3</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -743,115 +736,110 @@
         <v>205868</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="F6">
+    <row r="8" spans="1:13">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6">
+        <v>48.485</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.8106</v>
+      </c>
+      <c r="E10" s="6">
+        <v>39.3</v>
+      </c>
+      <c r="F10" s="6">
+        <v>39.79</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
+        <v>31.708</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="E11" s="6">
+        <v>47.88</v>
+      </c>
+      <c r="F11" s="6">
+        <v>48.83</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="8">
         <v>80.193</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5">
-        <v>48.485</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.8106</v>
-      </c>
-      <c r="E11" s="5">
-        <v>39.3</v>
-      </c>
-      <c r="F11" s="5">
-        <v>39.79</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="5">
-        <v>31.708</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="E12" s="5">
-        <v>47.88</v>
-      </c>
-      <c r="F12" s="5">
-        <v>48.83</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="7">
-        <v>80.193</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>87.18000000000001</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F12" s="8">
         <v>88.62</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G12" s="8">
         <v>1.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -212,17 +206,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Бургас</t>
   </si>
   <si>
     <t>ТУБАКон1</t>
@@ -77,21 +71,6 @@
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:24:00</t>
-  </si>
-  <si>
-    <t>11:11:00</t>
-  </si>
-  <si>
-    <t>3232109913 3232109913</t>
-  </si>
-  <si>
-    <t>3232201156 3232201156</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -511,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +499,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,195 +540,203 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>30.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>31.4</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>21.43</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H3">
+        <v>15.64</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J3">
+        <v>15.86</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>22.51</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H4">
+        <v>15.31</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J4">
+        <v>15.53</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>43.94</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.7044</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30.95</v>
+      </c>
+      <c r="F9" s="7">
+        <v>31.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>21.66</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>32.92</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>33.57</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="B10" s="7">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.54</v>
+      </c>
+      <c r="E10" s="7">
+        <v>30.8</v>
+      </c>
+      <c r="F10" s="7">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46163</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>23.81</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>18.57</v>
-      </c>
-      <c r="J3">
-        <v>0.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>18.81</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>137026</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7">
-        <v>23.81</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.7799</v>
-      </c>
-      <c r="E8" s="7">
-        <v>18.57</v>
-      </c>
-      <c r="F8" s="7">
-        <v>18.81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>21.66</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.5199</v>
-      </c>
-      <c r="E9" s="7">
-        <v>32.92</v>
-      </c>
-      <c r="F9" s="7">
-        <v>33.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="10">
-        <v>45.47</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>51.49</v>
-      </c>
-      <c r="F10" s="10">
-        <v>52.38</v>
+      <c r="B11" s="10">
+        <v>63.94</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>61.75</v>
+      </c>
+      <c r="F11" s="10">
+        <v>62.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -71,6 +77,15 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>07:51</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -490,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,10 +518,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,22 +557,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46176</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -572,25 +595,31 @@
       <c r="J2">
         <v>31.4</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>214547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46178</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>21.43</v>
@@ -607,25 +636,31 @@
       <c r="J3">
         <v>15.86</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>120244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46184</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>22.51</v>
@@ -642,13 +677,19 @@
       <c r="J4">
         <v>15.53</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M4">
+        <v>217570</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -656,18 +697,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -676,9 +717,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
         <v>43.94</v>
@@ -696,9 +737,9 @@
         <v>31.39</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
         <v>20</v>
@@ -716,9 +757,9 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B11" s="10">
         <v>63.94</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -49,18 +49,9 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Порт</t>
   </si>
   <si>
-    <t>Бургас</t>
-  </si>
-  <si>
     <t>ТУБАКон1</t>
   </si>
   <si>
@@ -79,13 +70,10 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>07:51</t>
+    <t>2026-06-16 10:10:29</t>
+  </si>
+  <si>
+    <t>2026-06-19 16:00:44</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -505,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,12 +506,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,227 +543,168 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>21.76</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H2">
+        <v>33.29</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>33.95</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3">
+        <v>22.94</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>14.91</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>15.14</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>30.8</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>31.4</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>214547</v>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7">
+        <v>22.94</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>14.91</v>
+      </c>
+      <c r="F8" s="7">
+        <v>15.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>21.43</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H3">
-        <v>15.64</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J3">
-        <v>15.86</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
+      <c r="B9" s="7">
+        <v>21.76</v>
+      </c>
+      <c r="C9" s="7">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>120244</v>
+      <c r="D9" s="8">
+        <v>1.5299</v>
+      </c>
+      <c r="E9" s="7">
+        <v>33.29</v>
+      </c>
+      <c r="F9" s="7">
+        <v>33.95</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>22.51</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H4">
-        <v>15.31</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J4">
-        <v>15.53</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>217570</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7">
-        <v>43.94</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B10" s="10">
+        <v>44.7</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D9" s="8">
-        <v>0.7044</v>
-      </c>
-      <c r="E9" s="7">
-        <v>30.95</v>
-      </c>
-      <c r="F9" s="7">
-        <v>31.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.54</v>
-      </c>
-      <c r="E10" s="7">
-        <v>30.8</v>
-      </c>
-      <c r="F10" s="7">
-        <v>31.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="10">
-        <v>63.94</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>61.75</v>
-      </c>
-      <c r="F11" s="10">
-        <v>62.79</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>48.2</v>
+      </c>
+      <c r="F10" s="10">
+        <v>49.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>ТУБАКон1</t>
@@ -70,10 +79,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 10:10:29</t>
-  </si>
-  <si>
-    <t>2026-06-19 16:00:44</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>3233434647 3233434647</t>
+  </si>
+  <si>
+    <t>3233592262 3233592262</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,14 +520,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,80 +564,107 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>21.76</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>33.29</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>33.95</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>22.94</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>0.65</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>14.91</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>15.14</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -624,29 +672,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7">
         <v>22.94</v>
@@ -664,9 +712,9 @@
         <v>15.14</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>21.76</v>
@@ -684,9 +732,9 @@
         <v>33.95</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B10" s="10">
         <v>44.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>ТУБАКон1</t>
@@ -79,19 +76,10 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:10:00</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
-    <t>3233434647 3233434647</t>
-  </si>
-  <si>
-    <t>3233592262 3233592262</t>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>16:01</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -511,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +508,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,101 +557,92 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>21.76</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>33.29</v>
       </c>
       <c r="I2" s="1">
-        <v>33.29</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
         <v>33.95</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
+        <v>219737</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>22.94</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>14.91</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>15.14</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>14.91</v>
-      </c>
-      <c r="J3">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
+        <v>221384</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -672,29 +650,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
         <v>22.94</v>
@@ -712,9 +690,9 @@
         <v>15.14</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7">
         <v>21.76</v>
@@ -732,9 +710,9 @@
         <v>33.95</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B10" s="10">
         <v>44.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,43 +55,37 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В0587ВТ</t>
   </si>
   <si>
-    <t>ТУБАКон1</t>
-  </si>
-  <si>
     <t>78970155027720832</t>
   </si>
   <si>
-    <t>78970155027720840</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>2026-07-01 18:03:00</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:30:59</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:35:12</t>
-  </si>
-  <si>
-    <t>2026-07-14 15:43:41</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:42:00</t>
+  </si>
+  <si>
+    <t>11:29:00</t>
+  </si>
+  <si>
+    <t>3235148672 3235148672</t>
+  </si>
+  <si>
+    <t>3235459795 3235459795</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -508,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,15 +514,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,250 +561,172 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>21.77</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>26.67</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
       <c r="H2">
-        <v>17.34</v>
+        <v>0.63</v>
       </c>
       <c r="I2" s="1">
-        <v>0.66</v>
+        <v>13.72</v>
       </c>
       <c r="J2">
-        <v>17.6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>13.93</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>139071</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46210</v>
+        <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>23.48</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="F3">
-        <v>15.64</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.62</v>
-      </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>14.79</v>
       </c>
       <c r="J3">
-        <v>9.85</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>138386</v>
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15.03</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>139389</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>30</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H4">
-        <v>44.1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J4">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="B8" s="7">
+        <v>45.25</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.6301</v>
+      </c>
+      <c r="E8" s="7">
+        <v>28.51</v>
+      </c>
+      <c r="F8" s="7">
+        <v>28.96</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>29.82</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H5">
-        <v>18.49</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J5">
-        <v>18.79</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>138726</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="s">
+    <row r="9" spans="1:14">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>72.13</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.6312</v>
-      </c>
-      <c r="E10" s="7">
-        <v>45.53</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="7">
-        <v>30</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.47</v>
-      </c>
-      <c r="E11" s="7">
-        <v>44.1</v>
-      </c>
-      <c r="F11" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="10">
-        <v>102.13</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>89.63</v>
-      </c>
-      <c r="F12" s="10">
-        <v>91.23999999999999</v>
+      <c r="B9" s="10">
+        <v>45.25</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>28.51</v>
+      </c>
+      <c r="F9" s="10">
+        <v>28.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -113,7 +113,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>0.6301</v>
+        <v>0.630055</v>
       </c>
       <c r="E8" s="7">
         <v>28.51</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,13 +521,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,98 +570,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>21.77</v>
+        <v>21.766</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.63</v>
       </c>
-      <c r="I2" s="1">
-        <v>13.72</v>
-      </c>
       <c r="J2">
+        <v>13.71258</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.64</v>
       </c>
-      <c r="K2" s="1">
-        <v>13.93</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>13.93024</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
         <v>139071</v>
       </c>
-      <c r="N2" t="s">
-        <v>22</v>
+      <c r="O2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>23.48</v>
+        <v>23.484</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>14.79</v>
-      </c>
       <c r="J3">
+        <v>14.79492</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>15.03</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>15.02976</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3">
         <v>139389</v>
       </c>
-      <c r="N3" t="s">
-        <v>23</v>
+      <c r="O3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -666,29 +678,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
         <v>45.25</v>
@@ -697,7 +709,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>0.630055</v>
+        <v>0.63</v>
       </c>
       <c r="E8" s="7">
         <v>28.51</v>
@@ -706,9 +718,9 @@
         <v>28.96</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
         <v>45.25</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -114,9 +111,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -210,10 +207,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,13 +518,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,107 +567,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>21.766</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>13.713</v>
+      </c>
+      <c r="J2">
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>13.93</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J2">
-        <v>13.71258</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L2" s="1">
-        <v>13.93024</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>139071</v>
       </c>
-      <c r="O2" t="s">
-        <v>23</v>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3">
         <v>23.484</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>14.795</v>
       </c>
       <c r="J3">
-        <v>14.79492</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>15.02976</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3">
+        <v>15.03</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
         <v>139389</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -678,49 +666,49 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7">
         <v>45.25</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
       <c r="D8" s="8">
         <v>0.63</v>
       </c>
-      <c r="E8" s="7">
-        <v>28.51</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="8">
+        <v>28.508</v>
+      </c>
+      <c r="F8" s="8">
         <v>28.96</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="10">
         <v>45.25</v>
@@ -730,7 +718,7 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="10">
-        <v>28.51</v>
+        <v>28.508</v>
       </c>
       <c r="F9" s="10">
         <v>28.96</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В0587ВТ</t>
@@ -73,19 +73,13 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:42:00</t>
-  </si>
-  <si>
-    <t>11:29:00</t>
-  </si>
-  <si>
-    <t>3235148672 3235148672</t>
-  </si>
-  <si>
-    <t>3235459795 3235459795</t>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>14:49</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -111,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -207,10 +201,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,17 +508,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,16 +557,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46224</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -585,39 +575,36 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>21.766</v>
-      </c>
-      <c r="G2" t="s">
+        <v>24.446</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H2">
+        <v>15.645</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="J2">
+        <v>15.89</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="H2">
-        <v>0.63</v>
-      </c>
-      <c r="I2" s="1">
-        <v>13.713</v>
-      </c>
-      <c r="J2">
-        <v>0.64</v>
-      </c>
-      <c r="K2" s="1">
-        <v>13.93</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
+      <c r="L2">
+        <v>139696</v>
       </c>
       <c r="M2">
-        <v>139071</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
+        <v>289119</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46231</v>
+        <v>46240</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -629,104 +616,142 @@
         <v>18</v>
       </c>
       <c r="F3">
-        <v>23.484</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
+        <v>25.364</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.63</v>
+        <v>16.487</v>
       </c>
       <c r="I3" s="1">
-        <v>14.795</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.03</v>
-      </c>
-      <c r="L3" t="s">
+        <v>16.74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>140017</v>
+      </c>
+      <c r="M3">
+        <v>243014</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>23.803</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>15.472</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>15.71</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="M3">
-        <v>139389</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="L4">
+        <v>140301</v>
+      </c>
+      <c r="M4">
+        <v>145761</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>73.613</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.64668</v>
+      </c>
+      <c r="E9" s="7">
+        <v>47.6</v>
+      </c>
+      <c r="F9" s="7">
+        <v>48.34</v>
+      </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="5" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>45.25</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E8" s="8">
-        <v>28.508</v>
-      </c>
-      <c r="F8" s="8">
-        <v>28.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="10">
-        <v>45.25</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>28.508</v>
-      </c>
-      <c r="F9" s="10">
-        <v>28.96</v>
+      <c r="B10" s="10">
+        <v>73.613</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>47.6</v>
+      </c>
+      <c r="F10" s="10">
+        <v>48.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,31 +58,64 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В0587ВТ</t>
   </si>
   <si>
+    <t>ТУБАКон1</t>
+  </si>
+  <si>
     <t>78970155027720832</t>
   </si>
   <si>
+    <t>78970155027720840</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>11:51</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>14:49</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:19:00</t>
+  </si>
+  <si>
+    <t>11:19:00</t>
+  </si>
+  <si>
+    <t>11:22:00</t>
+  </si>
+  <si>
+    <t>11:18:00</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>3236515555 3236515555</t>
+  </si>
+  <si>
+    <t>3236873138 3236873138</t>
+  </si>
+  <si>
+    <t>3236874791 3236874791</t>
+  </si>
+  <si>
+    <t>3236875913 3236875913</t>
+  </si>
+  <si>
+    <t>3237210077 3237210077</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КОНСТАНТИНОВО</t>
@@ -104,10 +140,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -187,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -201,10 +238,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,16 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,201 +597,321 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>26.64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>26.374</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>17.582</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>140617</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>24.446</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>15.645</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>15.89</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
-        <v>139696</v>
-      </c>
-      <c r="M2">
-        <v>289119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46240</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>25.364</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>16.487</v>
+        <v>6.37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.439</v>
       </c>
       <c r="I3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J3">
-        <v>16.74</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>140017</v>
+        <v>9.166</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>10.001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
       </c>
       <c r="M3">
-        <v>243014</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>140925</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>12.71</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="I4" s="1">
+        <v>18.29</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K4" s="1">
+        <v>19.955</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>23.44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I5" s="1">
+        <v>23.206</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15.47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>140925</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>23.803</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H4">
-        <v>15.472</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>21.67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I6" s="1">
+        <v>21.453</v>
+      </c>
+      <c r="J6" s="1">
         <v>0.66</v>
       </c>
-      <c r="J4">
-        <v>15.71</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="K6" s="1">
+        <v>14.302</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6">
+        <v>141214</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L4">
-        <v>140301</v>
-      </c>
-      <c r="M4">
-        <v>145761</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
+      <c r="B11" s="7">
+        <v>71.75</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.9900099999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>71.03</v>
+      </c>
+      <c r="F11" s="7">
+        <v>47.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>73.613</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.64668</v>
-      </c>
-      <c r="E9" s="7">
-        <v>47.6</v>
-      </c>
-      <c r="F9" s="7">
-        <v>48.34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="10">
-        <v>73.613</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>47.6</v>
-      </c>
-      <c r="F10" s="10">
-        <v>48.34</v>
+      <c r="B12" s="7">
+        <v>19.08</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.43899</v>
+      </c>
+      <c r="E12" s="7">
+        <v>27.46</v>
+      </c>
+      <c r="F12" s="7">
+        <v>29.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="11">
+        <v>90.83</v>
+      </c>
+      <c r="C13" s="12">
+        <v>5</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="11">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="F13" s="11">
+        <v>77.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КОНСТАНТИНОВО/КМЕТСТВО КОНСТАНТИНОВО.xlsx
@@ -624,10 +624,10 @@
         <v>23</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>26.374</v>
+        <v>17.316</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -668,10 +668,10 @@
         <v>23</v>
       </c>
       <c r="H3" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I3" s="1">
-        <v>9.166</v>
+        <v>9.81</v>
       </c>
       <c r="J3" s="1">
         <v>1.57</v>
@@ -712,10 +712,10 @@
         <v>23</v>
       </c>
       <c r="H4" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I4" s="1">
-        <v>18.29</v>
+        <v>19.573</v>
       </c>
       <c r="J4" s="1">
         <v>1.57</v>
@@ -756,10 +756,10 @@
         <v>23</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>23.206</v>
+        <v>15.236</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -800,10 +800,10 @@
         <v>23</v>
       </c>
       <c r="H6" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I6" s="1">
-        <v>21.453</v>
+        <v>14.086</v>
       </c>
       <c r="J6" s="1">
         <v>0.66</v>
@@ -862,10 +862,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="9">
-        <v>0.9900099999999999</v>
+        <v>0.65001</v>
       </c>
       <c r="E11" s="7">
-        <v>71.03</v>
+        <v>46.64</v>
       </c>
       <c r="F11" s="7">
         <v>47.35</v>
@@ -882,10 +882,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="9">
-        <v>1.43899</v>
+        <v>1.53999</v>
       </c>
       <c r="E12" s="7">
-        <v>27.46</v>
+        <v>29.38</v>
       </c>
       <c r="F12" s="7">
         <v>29.96</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="11">
-        <v>98.48999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F13" s="11">
         <v>77.31</v>
